--- a/data/SI/SI_3_data_gap_filling.xlsx
+++ b/data/SI/SI_3_data_gap_filling.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1480" documentId="13_ncr:1_{CE123D7F-5EB3-460B-B29F-F75C2D854814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD3AED12-14DD-4E07-ABF2-E46CC22DCC31}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -4371,10 +4371,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4642,10 +4638,10 @@
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="138.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="138.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="14.25" customHeight="1">
@@ -4656,7 +4652,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="17.25">
+    <row r="2" spans="1:2" ht="16.5">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -4664,7 +4660,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="66.75">
+    <row r="3" spans="1:2" ht="64">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -4712,13 +4708,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7443427-7747-4CC9-A5DE-F3ED143BBDED}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="68.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="65.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="68.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="65.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4741,7 +4737,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="30">
+    <row r="2" spans="1:6" ht="29">
       <c r="A2" s="6" t="s">
         <v>987</v>
       </c>
@@ -4755,7 +4751,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="45">
+    <row r="3" spans="1:6" ht="29">
       <c r="A3" s="6" t="s">
         <v>990</v>
       </c>
@@ -4820,7 +4816,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="30">
+    <row r="7" spans="1:6" ht="29">
       <c r="A7" s="6" t="s">
         <v>924</v>
       </c>
@@ -4854,7 +4850,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="45" customFormat="1" ht="60">
+    <row r="9" spans="1:6" s="45" customFormat="1" ht="58">
       <c r="A9" s="43" t="s">
         <v>920</v>
       </c>
@@ -4871,7 +4867,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="45" customFormat="1" ht="30">
+    <row r="10" spans="1:6" s="45" customFormat="1" ht="29">
       <c r="A10" s="43" t="s">
         <v>1011</v>
       </c>
@@ -4970,7 +4966,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="75">
+    <row r="16" spans="1:6" ht="72.5">
       <c r="A16" s="6" t="s">
         <v>1023</v>
       </c>
@@ -5060,11 +5056,11 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A219B65-17C1-432A-978C-0A30F412A7A0}">
   <dimension ref="A1:T167"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="81.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.81640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1">
@@ -5636,24 +5632,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003DBE41-F907-4509-8050-C24EEC72436D}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:Q77"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="62" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.1796875" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.26953125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1">
@@ -9682,23 +9678,23 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F859E1F8-BE29-4E42-8A84-A1C25096A0F3}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="66.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.26953125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.1796875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -11044,10 +11040,10 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:M43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -11252,16 +11248,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27A606A5-30AF-4421-9A6A-C93307FCE47D}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="65" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="197" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="139.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="139.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="255.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -11310,7 +11306,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -11333,7 +11329,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30">
+    <row r="4" spans="1:7" ht="29">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -11379,7 +11375,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30">
+    <row r="6" spans="1:7" ht="29">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -11457,19 +11453,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75EF5F87-1C2C-467D-A09B-6D158A412C6E}">
   <dimension ref="A1:N58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.1796875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.81640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="59" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="48" customFormat="1">
@@ -12929,7 +12925,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="30">
+    <row r="50" spans="1:10" ht="29">
       <c r="A50" s="8" t="s">
         <v>118</v>
       </c>
@@ -13195,18 +13191,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F494F318-26CF-4133-926D-9988560C1DA0}">
   <dimension ref="A1:M6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="59" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="48" customFormat="1">
@@ -13384,19 +13380,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F2820A0-2D63-4875-9A7D-5F54F0702DAC}">
   <dimension ref="A1:J29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="71.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="71.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1">
+    <row r="1" spans="1:10" ht="15" thickBot="1">
       <c r="A1" s="14" t="s">
         <v>158</v>
       </c>
@@ -13849,7 +13845,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.75" thickBot="1">
+    <row r="17" spans="1:10" ht="15" thickBot="1">
       <c r="A17" s="51" t="s">
         <v>154</v>
       </c>
@@ -13896,7 +13892,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15.75" thickBot="1">
+    <row r="19" spans="1:10" ht="15" thickBot="1">
       <c r="A19" s="51" t="s">
         <v>156</v>
       </c>
@@ -13917,7 +13913,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.75" thickBot="1">
+    <row r="20" spans="1:10" ht="15" thickBot="1">
       <c r="A20" s="52" t="s">
         <v>125</v>
       </c>
@@ -13938,7 +13934,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" thickBot="1">
+    <row r="21" spans="1:10" ht="15" thickBot="1">
       <c r="A21" s="53" t="s">
         <v>136</v>
       </c>
@@ -14140,7 +14136,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15.75" thickBot="1">
+    <row r="28" spans="1:10" ht="15" thickBot="1">
       <c r="A28" s="51" t="s">
         <v>137</v>
       </c>
@@ -14204,23 +14200,23 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D2E9A41-CA94-48A2-8537-40C2538A653B}">
   <dimension ref="A1:O233"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="58.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="62.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="66.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="47.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="92.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.81640625" customWidth="1"/>
+    <col min="6" max="6" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="62.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="38.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="66.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="47.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="92.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -23893,21 +23889,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A21299A7-BA99-47DC-BE65-0BC336460564}">
   <dimension ref="A1:N64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.1796875" customWidth="1"/>
     <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="56.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="110.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="56.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="110.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" customHeight="1">
@@ -24740,21 +24736,21 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3507E47D-9E60-48B6-807A-CA7E362AF30E}">
   <dimension ref="A1:M110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="74.28515625" customWidth="1"/>
-    <col min="3" max="3" width="53.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.42578125" customWidth="1"/>
-    <col min="5" max="5" width="35.140625" customWidth="1"/>
+    <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="74.26953125" customWidth="1"/>
+    <col min="3" max="3" width="53.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="73.453125" customWidth="1"/>
+    <col min="5" max="5" width="35.1796875" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.5703125" style="16" customWidth="1"/>
-    <col min="8" max="8" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.28515625" customWidth="1"/>
-    <col min="12" max="12" width="255.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="255.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.54296875" style="16" customWidth="1"/>
+    <col min="8" max="8" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.26953125" customWidth="1"/>
+    <col min="12" max="12" width="255.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="255.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1">
@@ -24830,7 +24826,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="30">
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="29">
       <c r="A3" t="s">
         <v>633</v>
       </c>
@@ -25145,7 +25141,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="30">
+    <row r="15" spans="1:13" ht="29">
       <c r="A15" t="s">
         <v>668</v>
       </c>
@@ -25177,7 +25173,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="45">
+    <row r="16" spans="1:13" ht="43.5">
       <c r="A16" t="s">
         <v>676</v>
       </c>
@@ -25218,7 +25214,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="30">
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>676</v>
       </c>
@@ -25346,7 +25342,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="30">
+    <row r="21" spans="1:13" ht="29">
       <c r="A21" t="s">
         <v>633</v>
       </c>
@@ -27168,7 +27164,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="45">
+    <row r="86" spans="1:12" ht="43.5">
       <c r="A86" t="s">
         <v>676</v>
       </c>
@@ -27335,7 +27331,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="30">
+    <row r="92" spans="1:12" ht="29">
       <c r="A92" t="s">
         <v>668</v>
       </c>
@@ -27367,7 +27363,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="30">
+    <row r="93" spans="1:12" ht="29">
       <c r="A93" t="s">
         <v>862</v>
       </c>
@@ -27882,21 +27878,21 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0BB7C2-416C-40BB-80A2-28B7CCA997D7}">
   <dimension ref="A1:N65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.1796875" customWidth="1"/>
     <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="56.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="110.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="56.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="110.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" customHeight="1">
